--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\RC_Partial\RC-Batch-Partial-Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F23C95-44B6-4941-AA01-E214FDCB0D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1992DB2-3545-4D54-8D74-F8D9C2CA9637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -225,6 +225,15 @@
   </si>
   <si>
     <t>VW_HappyPath_NF</t>
+  </si>
+  <si>
+    <t>VW_Discharge.txt</t>
+  </si>
+  <si>
+    <t>VW Discharge Input File</t>
+  </si>
+  <si>
+    <t>VW_HappyPath_Discharge</t>
   </si>
 </sst>
 </file>
@@ -274,7 +283,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -611,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
@@ -976,25 +995,54 @@
         <v>60</v>
       </c>
     </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="P13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>62</v>
+      </c>
+      <c r="R13" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="A1:A2 A13:A1048576">
+  <conditionalFormatting sqref="A1:A2 A14:A1048576">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
+  <conditionalFormatting sqref="A4">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
+  <conditionalFormatting sqref="A5:A7">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A7">
+  <conditionalFormatting sqref="A8:A11">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8:A11">
+  <conditionalFormatting sqref="A12:A13">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RC-PARTIAL-BATCHFILE\RC-Partial\RC-Batch-Partial-Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\RC_Partial\RC-Batch-Partial-Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6826CEF7-B5DB-4299-8FAD-0AE97B0E7F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4B0CF9-E58F-494F-BCF1-6F108AEAD7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,9 +124,6 @@
     <t>Ford_NF.fc</t>
   </si>
   <si>
-    <t>BNS_COMM_HappyPath_NF</t>
-  </si>
-  <si>
     <t>BNS_COMM</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
     <t>BNS_Comm_Renewal.xml</t>
   </si>
   <si>
-    <t>BNS_COMM_AmendmentHappyPath</t>
-  </si>
-  <si>
     <t>BNS_Comm_Amendment.xml</t>
   </si>
   <si>
@@ -236,6 +230,12 @@
   </si>
   <si>
     <t>CC_NF.dx2</t>
+  </si>
+  <si>
+    <t>BNS_COMM_AmendmentHappyPath_NF</t>
+  </si>
+  <si>
+    <t>BNS_COMM_AmendmentHappyPath_Amendment</t>
   </si>
 </sst>
 </file>
@@ -613,7 +613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.8984375" customWidth="1"/>
@@ -640,7 +640,7 @@
     <col min="23" max="23" width="18.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -734,7 +734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -754,284 +754,284 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
         <v>35</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" t="s">
         <v>36</v>
       </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="R7" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="B8" t="s">
         <v>44</v>
       </c>
-      <c r="P7" t="s">
-        <v>37</v>
-      </c>
-      <c r="R7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
         <v>48</v>
       </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="O9" t="s">
         <v>49</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
         <v>46</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
         <v>46</v>
       </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" t="s">
-        <v>50</v>
-      </c>
-      <c r="O9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>54</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="T11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-      <c r="S11" t="s">
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>57</v>
       </c>
-      <c r="T11" t="s">
+      <c r="B12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
         <v>60</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" t="s">
         <v>61</v>
       </c>
-      <c r="E12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="Q13" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="R13" t="s">
         <v>64</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>65</v>
-      </c>
-      <c r="R13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
         <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>70</v>
       </c>
       <c r="F14" t="s">
         <v>27</v>
@@ -1040,7 +1040,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W13" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:W3 A8:W13 B7:D7 F7:W7 A5:W6 B4:W4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\march_5\RC-Batch-Partial-Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\mar13\RC-Batch-Partial-Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F06BD76-FD3E-479C-A800-7A9460D64CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2367EBFB-4578-4843-B4A0-4292D5FEED91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="75">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -236,6 +236,18 @@
   </si>
   <si>
     <t>BNS_COMM_NFHappyPath</t>
+  </si>
+  <si>
+    <t>BNS_COMM_SearchHappyPath</t>
+  </si>
+  <si>
+    <t>BNS_Comm_Search.xml</t>
+  </si>
+  <si>
+    <t>BNS_COMM_LookupHappyPath</t>
+  </si>
+  <si>
+    <t>BNS_Comm_Lookup.xml</t>
   </si>
 </sst>
 </file>
@@ -612,13 +624,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -668,7 +681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -691,7 +704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -711,7 +724,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -734,7 +747,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -763,7 +776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -792,7 +805,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -821,7 +834,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -841,7 +854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -867,7 +880,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -896,7 +909,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -922,7 +935,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -951,7 +964,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -974,7 +987,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1003,7 +1016,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -1023,7 +1036,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -1046,7 +1059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -1066,13 +1079,59 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P15 A16:P16" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P15 B16:P16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\mar13\RC-Batch-Partial-Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Mar16\RC-Batch-Partial-Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2367EBFB-4578-4843-B4A0-4292D5FEED91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2975CC4F-A7FC-4CAB-AF14-73DFF113FB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="85">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -248,6 +248,36 @@
   </si>
   <si>
     <t>BNS_Comm_Lookup.xml</t>
+  </si>
+  <si>
+    <t>GMF</t>
+  </si>
+  <si>
+    <t>GMFCL</t>
+  </si>
+  <si>
+    <t>GMF_CL</t>
+  </si>
+  <si>
+    <t>GMFCL_HappyPath.XIF</t>
+  </si>
+  <si>
+    <t>GMF_ReturnFile</t>
+  </si>
+  <si>
+    <t>GMFCL_NFHappyPath</t>
+  </si>
+  <si>
+    <t>GMFCR</t>
+  </si>
+  <si>
+    <t>GMF_CR</t>
+  </si>
+  <si>
+    <t>GMFCR_HappyPath.XIF</t>
+  </si>
+  <si>
+    <t>GMFCR_NFHappyPath</t>
   </si>
 </sst>
 </file>
@@ -289,7 +319,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -624,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
@@ -1128,7 +1179,59 @@
         <v>30</v>
       </c>
     </row>
+    <row r="20" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:P15 B16:P16" numberStoredAsText="1"/>

--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Mar16\RC-Batch-Partial-Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Mar_17\RC-Batch-Partial-Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2975CC4F-A7FC-4CAB-AF14-73DFF113FB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44AC38C-2E9D-42B7-A781-F2B4674BFBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="88">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -278,6 +278,15 @@
   </si>
   <si>
     <t>GMFCR_NFHappyPath</t>
+  </si>
+  <si>
+    <t>BNS_Comm_Amend.xml</t>
+  </si>
+  <si>
+    <t>BNS_COMM_NF</t>
+  </si>
+  <si>
+    <t>BNS_COMM_Amendment</t>
   </si>
 </sst>
 </file>
@@ -675,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
@@ -1110,7 +1119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -1133,7 +1142,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -1156,7 +1165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>73</v>
       </c>
@@ -1179,7 +1188,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -1202,7 +1211,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -1223,6 +1232,58 @@
       </c>
       <c r="G21" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>28</v>
+      </c>
+      <c r="K22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Mar_17\RC-Batch-Partial-Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Mar18\RC_Batch_Full_Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44AC38C-2E9D-42B7-A781-F2B4674BFBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865E4784-ED08-4307-89E4-40C0F97318D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="91">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -287,6 +287,15 @@
   </si>
   <si>
     <t>BNS_COMM_Amendment</t>
+  </si>
+  <si>
+    <t>BNS_COMM_NF_Duplicate_BatchNumber</t>
+  </si>
+  <si>
+    <t>BNS_COMM_Renewal_Duplicate_BatchNumber</t>
+  </si>
+  <si>
+    <t>BNS_COMM_Discharge_Duplicate_BatchNumber</t>
   </si>
 </sst>
 </file>
@@ -684,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
@@ -1286,6 +1295,87 @@
         <v>30</v>
       </c>
     </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A20">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
@@ -1294,6 +1384,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:P15 B16:P16" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Mar18\RC_Batch_Full_Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Full\Mar19\RC_Batch_Full_Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865E4784-ED08-4307-89E4-40C0F97318D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391733B3-32D0-4CF5-9E2A-139B93ADD709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="InputFileInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InputFileInfo!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InputFileInfo!$A$1:$P$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="99">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -296,6 +296,30 @@
   </si>
   <si>
     <t>BNS_COMM_Discharge_Duplicate_BatchNumber</t>
+  </si>
+  <si>
+    <t>BNS_COMM_NF_Invalid_BatchFile</t>
+  </si>
+  <si>
+    <t>BNS_COMM_Discharge_Invalid_BatchFile</t>
+  </si>
+  <si>
+    <t>BNS_COMM_Renewal_Invalid_BatchFile</t>
+  </si>
+  <si>
+    <t>BNS_COMM_External_Invalid_BatchFile</t>
+  </si>
+  <si>
+    <t>BNS_COMM_Lookup_Invalid_BatchFile</t>
+  </si>
+  <si>
+    <t>BNS_COMM_Amendment_Invalid_BatchFile</t>
+  </si>
+  <si>
+    <t>BNS_COMM_NF_OwnerType_Customer</t>
+  </si>
+  <si>
+    <t>BNS_Comm_NF_Customer.xml</t>
   </si>
 </sst>
 </file>
@@ -693,7 +717,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P26"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
@@ -750,7 +775,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -773,7 +798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -903,7 +928,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -923,7 +948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -949,7 +974,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -978,7 +1003,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1004,7 +1029,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1033,7 +1058,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1056,7 +1081,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1085,7 +1110,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -1197,7 +1222,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -1220,7 +1245,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -1376,7 +1401,193 @@
         <v>35</v>
       </c>
     </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" t="s">
+        <v>28</v>
+      </c>
+      <c r="K32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:P32" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="BNS_COMM"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A20">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>

--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Full\Mar19\RC_Batch_Full_Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Full\Mar23\RC_Batch_Full_Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391733B3-32D0-4CF5-9E2A-139B93ADD709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D83A6C5-6977-41AF-A729-01248F7348C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="105">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -320,6 +320,24 @@
   </si>
   <si>
     <t>BNS_Comm_NF_Customer.xml</t>
+  </si>
+  <si>
+    <t>BNS_Comm_NF_Term99.xml</t>
+  </si>
+  <si>
+    <t>BNS_COMM_NF_Term99</t>
+  </si>
+  <si>
+    <t>BNS_COMM_NF_QC</t>
+  </si>
+  <si>
+    <t>BNS_Comm_NF_QC.xml</t>
+  </si>
+  <si>
+    <t>BNS_COMM_NF_Invalid_TransitNumber</t>
+  </si>
+  <si>
+    <t>BNS_Comm_NF_Invalid.xml</t>
   </si>
 </sst>
 </file>
@@ -718,7 +736,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
@@ -1577,6 +1595,75 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
         <v>30</v>
       </c>
     </row>

--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Full\Mar23\RC_Batch_Full_Regression\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Full_reg\RC_Batch_Full_Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D83A6C5-6977-41AF-A729-01248F7348C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BD3D4F-C234-434A-BF9D-FA74FC717620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,15 @@
     <sheet name="InputFileInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InputFileInfo!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InputFileInfo!$A$1:$P$36</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="134">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -338,6 +339,93 @@
   </si>
   <si>
     <t>BNS_Comm_NF_Invalid.xml</t>
+  </si>
+  <si>
+    <t>TDAF_SLAReport</t>
+  </si>
+  <si>
+    <t>ClientSLAReport</t>
+  </si>
+  <si>
+    <t>TDAF_Handshakefile</t>
+  </si>
+  <si>
+    <t>TDAF_Invalid_Batch_File_NF</t>
+  </si>
+  <si>
+    <t>TDAF_Invalid_Batch_File_Renewal</t>
+  </si>
+  <si>
+    <t>TDAF_Invalid_Batch_File_Discharge</t>
+  </si>
+  <si>
+    <t>TDAF_Duplicate_BatchNumber_NF</t>
+  </si>
+  <si>
+    <t>TDAF_Duplicate_BatchNumber_Renewal</t>
+  </si>
+  <si>
+    <t>TDAF_Duplicate_BatchNumber_Discharge</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_AB</t>
+  </si>
+  <si>
+    <t>tdaf_ab</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_BC</t>
+  </si>
+  <si>
+    <t>tdaf_BC</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_SK</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_MB</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_ON</t>
+  </si>
+  <si>
+    <t>tdaf_sk</t>
+  </si>
+  <si>
+    <t>tdaf_mb</t>
+  </si>
+  <si>
+    <t>tdaf_on</t>
+  </si>
+  <si>
+    <t>tdaf_qc</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_QC</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_MissingTerm</t>
+  </si>
+  <si>
+    <t>tdaf_missing_Term</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_QC_Term</t>
+  </si>
+  <si>
+    <t>tdaf_qc_term</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_Term_99Years</t>
+  </si>
+  <si>
+    <t>tdaf_99_Years</t>
+  </si>
+  <si>
+    <t>tdaf_Term_Rounded</t>
+  </si>
+  <si>
+    <t>TDAF_HappyPath_Term_Rounded</t>
   </si>
 </sst>
 </file>
@@ -736,11 +824,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -836,7 +925,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -859,7 +948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -888,7 +977,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -917,7 +1006,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -946,7 +1035,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -966,7 +1055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -992,7 +1081,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -1021,7 +1110,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1047,7 +1136,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1148,7 +1237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -1171,7 +1260,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -1194,7 +1283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -1217,7 +1306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>73</v>
       </c>
@@ -1286,7 +1375,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -1315,7 +1404,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -1338,7 +1427,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>88</v>
       </c>
@@ -1361,7 +1450,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -1390,7 +1479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>90</v>
       </c>
@@ -1419,7 +1508,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -1442,7 +1531,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>92</v>
       </c>
@@ -1471,7 +1560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>93</v>
       </c>
@@ -1500,7 +1589,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -1523,7 +1612,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>95</v>
       </c>
@@ -1546,7 +1635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -1575,7 +1664,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>97</v>
       </c>
@@ -1598,7 +1687,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>100</v>
       </c>
@@ -1621,7 +1710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -1644,7 +1733,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -1667,11 +1756,401 @@
         <v>30</v>
       </c>
     </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s">
+        <v>43</v>
+      </c>
+      <c r="L40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
+        <v>43</v>
+      </c>
+      <c r="L43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>46</v>
+      </c>
+      <c r="H44" t="s">
+        <v>47</v>
+      </c>
+      <c r="I44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" t="s">
+        <v>117</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" t="s">
+        <v>121</v>
+      </c>
+      <c r="F47" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" t="s">
+        <v>123</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" t="s">
+        <v>124</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" t="s">
+        <v>127</v>
+      </c>
+      <c r="F51" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" t="s">
+        <v>129</v>
+      </c>
+      <c r="F52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>133</v>
+      </c>
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" t="s">
+        <v>132</v>
+      </c>
+      <c r="F54" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P32" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:P36" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="BNS_COMM"/>
+        <filter val="TDAF"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1684,7 +2163,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P15 B16:P16" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P7 B16:P16 A12:P15 B11:P11 A9:P10 B8:P8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/TestData.xlsx
+++ b/src/data/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcharles\source\Repository\CDBatch_Migration\Full_reg\RC_Batch_Full_Regression\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BD3D4F-C234-434A-BF9D-FA74FC717620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1F7E3A-59B7-4B89-AFBD-E4974D1783E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,14 @@
     <sheet name="InputFileInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InputFileInfo!$A$1:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InputFileInfo!$A$1:$P$54</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="139">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -215,15 +214,9 @@
     <t>VW Discharge Input File</t>
   </si>
   <si>
-    <t>clearcharge_HappyPath</t>
-  </si>
-  <si>
     <t>CLEARCHARGE</t>
   </si>
   <si>
-    <t>CLEARCHARGE Billing Input File</t>
-  </si>
-  <si>
     <t>CC_NF.dx2</t>
   </si>
   <si>
@@ -426,6 +419,27 @@
   </si>
   <si>
     <t>TDAF_HappyPath_Term_Rounded</t>
+  </si>
+  <si>
+    <t>TDAF_NF_COP</t>
+  </si>
+  <si>
+    <t>Clear Charge Billing File</t>
+  </si>
+  <si>
+    <t>ClearCharge_HappyPath</t>
+  </si>
+  <si>
+    <t>TDAF_Duplicate_FileName_NF</t>
+  </si>
+  <si>
+    <t>TDAF_Duplicate_FileName_Renewal</t>
+  </si>
+  <si>
+    <t>TDAF_Duplicate_FileName_Discharge</t>
+  </si>
+  <si>
+    <t>TDAF_Duplicate_FileName_ChangeOfProvince</t>
   </si>
 </sst>
 </file>
@@ -824,12 +838,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -1124,7 +1141,7 @@
         <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
@@ -1219,19 +1236,19 @@
     </row>
     <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" t="s">
         <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -1239,22 +1256,22 @@
     </row>
     <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" t="s">
         <v>67</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
@@ -1262,7 +1279,7 @@
     </row>
     <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
@@ -1285,7 +1302,7 @@
     </row>
     <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1297,7 +1314,7 @@
         <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
@@ -1308,7 +1325,7 @@
     </row>
     <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
@@ -1320,7 +1337,7 @@
         <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -1331,53 +1348,53 @@
     </row>
     <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
         <v>75</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>76</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
         <v>77</v>
-      </c>
-      <c r="E20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" t="s">
         <v>81</v>
       </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>83</v>
-      </c>
       <c r="F21" t="s">
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -1401,12 +1418,12 @@
         <v>28</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
@@ -1429,7 +1446,7 @@
     </row>
     <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
@@ -1452,7 +1469,7 @@
     </row>
     <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -1481,7 +1498,7 @@
     </row>
     <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
@@ -1510,7 +1527,7 @@
     </row>
     <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -1533,7 +1550,7 @@
     </row>
     <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
@@ -1562,7 +1579,7 @@
     </row>
     <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
@@ -1591,7 +1608,7 @@
     </row>
     <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
@@ -1603,10 +1620,10 @@
         <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G30" t="s">
         <v>30</v>
@@ -1614,7 +1631,7 @@
     </row>
     <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
@@ -1626,7 +1643,7 @@
         <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -1637,7 +1654,7 @@
     </row>
     <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
@@ -1661,12 +1678,12 @@
         <v>28</v>
       </c>
       <c r="K32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
         <v>27</v>
@@ -1678,7 +1695,7 @@
         <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
@@ -1689,7 +1706,7 @@
     </row>
     <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
         <v>27</v>
@@ -1701,7 +1718,7 @@
         <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F34" t="s">
         <v>20</v>
@@ -1712,7 +1729,7 @@
     </row>
     <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
@@ -1724,7 +1741,7 @@
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F35" t="s">
         <v>20</v>
@@ -1735,7 +1752,7 @@
     </row>
     <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
         <v>27</v>
@@ -1747,7 +1764,7 @@
         <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F36" t="s">
         <v>20</v>
@@ -1758,7 +1775,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
         <v>39</v>
@@ -1773,12 +1790,12 @@
         <v>41</v>
       </c>
       <c r="F37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
         <v>39</v>
@@ -1798,7 +1815,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
         <v>39</v>
@@ -1818,7 +1835,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
         <v>39</v>
@@ -1844,7 +1861,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
         <v>39</v>
@@ -1873,7 +1890,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B42" t="s">
         <v>39</v>
@@ -1893,7 +1910,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
         <v>39</v>
@@ -1919,7 +1936,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B44" t="s">
         <v>39</v>
@@ -1948,7 +1965,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B45" t="s">
         <v>39</v>
@@ -1960,7 +1977,7 @@
         <v>40</v>
       </c>
       <c r="E45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F45" t="s">
         <v>20</v>
@@ -1968,7 +1985,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
         <v>39</v>
@@ -1980,7 +1997,7 @@
         <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F46" t="s">
         <v>20</v>
@@ -1988,7 +2005,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
         <v>39</v>
@@ -2000,7 +2017,7 @@
         <v>40</v>
       </c>
       <c r="E47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F47" t="s">
         <v>20</v>
@@ -2008,7 +2025,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B48" t="s">
         <v>39</v>
@@ -2020,134 +2037,235 @@
         <v>40</v>
       </c>
       <c r="E48" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" t="s">
         <v>122</v>
       </c>
-      <c r="F48" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>120</v>
-      </c>
-      <c r="B49" t="s">
-        <v>39</v>
-      </c>
-      <c r="C49" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" t="s">
-        <v>40</v>
-      </c>
-      <c r="E49" t="s">
-        <v>123</v>
-      </c>
-      <c r="F49" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" t="s">
         <v>125</v>
       </c>
-      <c r="B50" t="s">
-        <v>39</v>
-      </c>
-      <c r="C50" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" t="s">
-        <v>124</v>
-      </c>
-      <c r="F50" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="F51" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>126</v>
       </c>
-      <c r="B51" t="s">
-        <v>39</v>
-      </c>
-      <c r="C51" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" t="s">
-        <v>40</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" t="s">
         <v>127</v>
       </c>
-      <c r="F51" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="F52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>128</v>
       </c>
-      <c r="B52" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" t="s">
-        <v>40</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" t="s">
         <v>129</v>
       </c>
-      <c r="F52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="F53" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" t="s">
         <v>130</v>
       </c>
-      <c r="B53" t="s">
-        <v>39</v>
-      </c>
-      <c r="C53" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" t="s">
-        <v>40</v>
-      </c>
-      <c r="E53" t="s">
-        <v>131</v>
-      </c>
-      <c r="F53" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>133</v>
-      </c>
-      <c r="B54" t="s">
-        <v>39</v>
-      </c>
-      <c r="C54" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54" t="s">
-        <v>40</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55" t="s">
+        <v>41</v>
+      </c>
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" t="s">
+        <v>40</v>
+      </c>
+      <c r="E56" t="s">
+        <v>41</v>
+      </c>
+      <c r="F56" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s">
+        <v>43</v>
+      </c>
+      <c r="L56" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" t="s">
+        <v>41</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>46</v>
+      </c>
+      <c r="H57" t="s">
+        <v>47</v>
+      </c>
+      <c r="I57" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E58" t="s">
         <v>132</v>
       </c>
-      <c r="F54" t="s">
-        <v>20</v>
+      <c r="F58" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58" t="s">
+        <v>50</v>
+      </c>
+      <c r="N58" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P36" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:P54" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
         <filter val="TDAF"/>
@@ -2163,7 +2281,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P7 B16:P16 A12:P15 B11:P11 A9:P10 B8:P8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P7 B16:P16 A12:P14 B11:D11 A9:P10 B8:P8 F11:P11 B15:C15 F15:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>